--- a/docs/d/53/inyear.xlsx
+++ b/docs/d/53/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 76 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 73 clubs short</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>10</v>
@@ -1612,8 +1612,8 @@
       <c r="R9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S9" s="9" t="n">
-        <v>1</v>
+      <c r="S9" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T9" s="9" t="n">
         <v>0</v>
@@ -4752,7 +4752,7 @@
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" s="6" t="n">
         <v>10</v>
@@ -4822,8 +4822,8 @@
       <c r="Y40" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z40" s="9" t="n">
-        <v>0</v>
+      <c r="Z40" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA40" s="10" t="n">
         <v>1</v>
@@ -7220,7 +7220,7 @@
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>10</v>
@@ -7234,13 +7234,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
         <v>0</v>
       </c>
       <c r="V64" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W64" s="9" t="n">
         <v>0</v>
@@ -7290,8 +7290,8 @@
       <c r="Y64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z64" s="9" t="n">
-        <v>0</v>
+      <c r="Z64" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA64" s="10" t="n">
         <v>1</v>
@@ -8683,7 +8683,7 @@
         </is>
       </c>
       <c r="P78" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q78" s="9" t="n">
         <v>0</v>
@@ -8787,7 +8787,7 @@
         <v>1</v>
       </c>
       <c r="Q79" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R79" s="9" t="n">
         <v>0</v>
@@ -11735,7 +11735,7 @@
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11805,8 +11805,8 @@
       <c r="Y109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z109" s="9" t="n">
-        <v>0</v>
+      <c r="Z109" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA109" s="10" t="n">
         <v>1</v>
@@ -13517,7 +13517,7 @@
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>10</v>
@@ -13569,8 +13569,8 @@
       <c r="S127" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T127" s="9" t="n">
-        <v>0</v>
+      <c r="T127" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U127" s="9" t="n">
         <v>0</v>
@@ -16489,7 +16489,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -16720,7 +16720,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -16918,7 +16918,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -17248,7 +17248,7 @@
         <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -17380,7 +17380,7 @@
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>

--- a/docs/d/53/inyear.xlsx
+++ b/docs/d/53/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5754,11 @@
       <c r="AB49" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC49" s="4" t="inlineStr"/>
+      <c r="AC49" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -8822,7 +8826,11 @@
       <c r="AB79" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC79" s="4" t="inlineStr"/>
+      <c r="AC79" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">

--- a/docs/d/53/inyear.xlsx
+++ b/docs/d/53/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 2 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 2 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 73 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 65 clubs short</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>10</v>
@@ -1818,8 +1818,8 @@
       <c r="R11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S11" s="9" t="n">
-        <v>1</v>
+      <c r="S11" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T11" s="10" t="n">
         <v>1</v>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -3075,8 +3075,8 @@
       <c r="Y23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z23" s="9" t="n">
-        <v>0</v>
+      <c r="Z23" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA23" s="10" t="n">
         <v>1</v>
@@ -3726,7 +3726,7 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>10</v>
@@ -3778,8 +3778,8 @@
       <c r="S30" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="T30" s="9" t="n">
-        <v>0</v>
+      <c r="T30" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U30" s="9" t="n">
         <v>0</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4511,8 +4511,8 @@
       <c r="Y37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z37" s="9" t="n">
-        <v>0</v>
+      <c r="Z37" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA37" s="10" t="n">
         <v>1</v>
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="P44" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q44" s="9" t="n">
         <v>1</v>
@@ -5208,7 +5208,7 @@
         <v>0</v>
       </c>
       <c r="S44" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T44" s="9" t="n">
         <v>0</v>
@@ -7024,7 +7024,7 @@
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -7094,8 +7094,8 @@
       <c r="Y62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z62" s="9" t="n">
-        <v>0</v>
+      <c r="Z62" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA62" s="10" t="n">
         <v>1</v>
@@ -8444,7 +8444,7 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8514,8 +8514,8 @@
       <c r="Y76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z76" s="9" t="n">
-        <v>0</v>
+      <c r="Z76" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA76" s="10" t="n">
         <v>1</v>
@@ -10753,7 +10753,7 @@
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10823,8 +10823,8 @@
       <c r="Y99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z99" s="9" t="n">
-        <v>0</v>
+      <c r="Z99" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA99" s="10" t="n">
         <v>1</v>
@@ -11091,7 +11091,7 @@
         </is>
       </c>
       <c r="P102" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q102" s="9" t="n">
         <v>1</v>
@@ -12337,7 +12337,7 @@
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -12351,13 +12351,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
@@ -12380,8 +12380,8 @@
       <c r="P115" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q115" s="9" t="n">
-        <v>1</v>
+      <c r="Q115" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R115" s="9" t="n">
         <v>0</v>
@@ -12395,8 +12395,8 @@
       <c r="U115" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V115" s="9" t="n">
-        <v>3</v>
+      <c r="V115" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W115" s="9" t="n">
         <v>0</v>
@@ -12549,13 +12549,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>0</v>
       </c>
       <c r="V117" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W117" s="9" t="n">
         <v>0</v>
@@ -12733,7 +12733,7 @@
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12803,8 +12803,8 @@
       <c r="Y119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z119" s="9" t="n">
-        <v>0</v>
+      <c r="Z119" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA119" s="10" t="n">
         <v>1</v>
@@ -14361,7 +14361,7 @@
         <v>1</v>
       </c>
       <c r="Q135" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R135" s="9" t="n">
         <v>0</v>
@@ -15010,7 +15010,7 @@
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F142" s="6" t="n">
         <v>10</v>
@@ -15080,8 +15080,8 @@
       <c r="Y142" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z142" s="9" t="n">
-        <v>0</v>
+      <c r="Z142" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA142" s="10" t="n">
         <v>1</v>
@@ -16297,7 +16297,7 @@
         </is>
       </c>
       <c r="E155" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F155" s="6" t="n">
         <v>10</v>
@@ -16367,8 +16367,8 @@
       <c r="Y155" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z155" s="9" t="n">
-        <v>0</v>
+      <c r="Z155" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA155" s="10" t="n">
         <v>1</v>
@@ -16530,7 +16530,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -16596,7 +16596,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -16662,7 +16662,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -16728,7 +16728,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -16992,7 +16992,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -17157,7 +17157,7 @@
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -17289,13 +17289,13 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -17322,7 +17322,7 @@
         <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -17487,7 +17487,7 @@
         <v>6</v>
       </c>
       <c r="D33" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -17553,7 +17553,7 @@
         <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>

--- a/docs/d/53/inyear.xlsx
+++ b/docs/d/53/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 2 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 2 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 65 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 35 clubs short</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>10</v>
@@ -1330,8 +1330,8 @@
       <c r="Y6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z6" s="9" t="n">
-        <v>0</v>
+      <c r="Z6" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA6" s="10" t="n">
         <v>1</v>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>10</v>
@@ -1431,8 +1431,8 @@
       <c r="Y7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z7" s="9" t="n">
-        <v>0</v>
+      <c r="Z7" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA7" s="10" t="n">
         <v>1</v>
@@ -1462,7 +1462,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>10</v>
@@ -1532,8 +1532,8 @@
       <c r="Y8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z8" s="9" t="n">
-        <v>0</v>
+      <c r="Z8" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA8" s="10" t="n">
         <v>1</v>
@@ -1979,7 +1979,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -2049,8 +2049,8 @@
       <c r="Y13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z13" s="9" t="n">
-        <v>0</v>
+      <c r="Z13" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA13" s="10" t="n">
         <v>1</v>
@@ -2181,7 +2181,7 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>10</v>
@@ -2251,8 +2251,8 @@
       <c r="Y15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z15" s="9" t="n">
-        <v>0</v>
+      <c r="Z15" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA15" s="10" t="n">
         <v>1</v>
@@ -2589,7 +2589,7 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>10</v>
@@ -2659,8 +2659,8 @@
       <c r="Y19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z19" s="9" t="n">
-        <v>0</v>
+      <c r="Z19" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA19" s="10" t="n">
         <v>1</v>
@@ -3310,7 +3310,7 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>10</v>
@@ -3380,8 +3380,8 @@
       <c r="Y26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z26" s="9" t="n">
-        <v>0</v>
+      <c r="Z26" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA26" s="10" t="n">
         <v>1</v>
@@ -4387,7 +4387,7 @@
         <v>2</v>
       </c>
       <c r="R36" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S36" s="9" t="n">
         <v>1</v>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>10</v>
@@ -4721,8 +4721,8 @@
       <c r="Y39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z39" s="9" t="n">
-        <v>0</v>
+      <c r="Z39" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA39" s="10" t="n">
         <v>1</v>
@@ -4853,7 +4853,7 @@
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F41" s="6" t="n">
         <v>10</v>
@@ -4923,8 +4923,8 @@
       <c r="Y41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z41" s="9" t="n">
-        <v>0</v>
+      <c r="Z41" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA41" s="10" t="n">
         <v>1</v>
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -6165,8 +6165,8 @@
       <c r="Y53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z53" s="9" t="n">
-        <v>0</v>
+      <c r="Z53" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA53" s="10" t="n">
         <v>1</v>
@@ -6443,7 +6443,7 @@
         </is>
       </c>
       <c r="P56" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q56" s="9" t="n">
         <v>0</v>
@@ -7038,13 +7038,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
@@ -7083,7 +7083,7 @@
         <v>0</v>
       </c>
       <c r="V62" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W62" s="9" t="n">
         <v>0</v>
@@ -7123,7 +7123,7 @@
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -7193,8 +7193,8 @@
       <c r="Y63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z63" s="9" t="n">
-        <v>0</v>
+      <c r="Z63" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA63" s="10" t="n">
         <v>1</v>
@@ -7325,7 +7325,7 @@
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -7395,8 +7395,8 @@
       <c r="Y65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z65" s="9" t="n">
-        <v>0</v>
+      <c r="Z65" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA65" s="10" t="n">
         <v>1</v>
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>10</v>
@@ -7904,8 +7904,8 @@
       <c r="Y70" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z70" s="9" t="n">
-        <v>0</v>
+      <c r="Z70" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA70" s="10" t="n">
         <v>1</v>
@@ -8036,7 +8036,7 @@
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>10</v>
@@ -8106,8 +8106,8 @@
       <c r="Y72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z72" s="9" t="n">
-        <v>0</v>
+      <c r="Z72" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA72" s="10" t="n">
         <v>1</v>
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>10</v>
@@ -9023,8 +9023,8 @@
       <c r="Y81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z81" s="9" t="n">
-        <v>0</v>
+      <c r="Z81" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA81" s="10" t="n">
         <v>1</v>
@@ -9054,7 +9054,7 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -9124,8 +9124,8 @@
       <c r="Y82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z82" s="9" t="n">
-        <v>0</v>
+      <c r="Z82" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA82" s="10" t="n">
         <v>1</v>
@@ -9301,7 +9301,7 @@
         </is>
       </c>
       <c r="P84" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q84" s="9" t="n">
         <v>0</v>
@@ -9464,7 +9464,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -9534,8 +9534,8 @@
       <c r="Y86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z86" s="9" t="n">
-        <v>0</v>
+      <c r="Z86" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA86" s="10" t="n">
         <v>1</v>
@@ -9975,13 +9975,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>0</v>
       </c>
       <c r="V91" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W91" s="9" t="n">
         <v>0</v>
@@ -10357,7 +10357,7 @@
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -10427,8 +10427,8 @@
       <c r="Y95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z95" s="9" t="n">
-        <v>0</v>
+      <c r="Z95" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA95" s="10" t="n">
         <v>1</v>
@@ -10654,7 +10654,7 @@
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10724,8 +10724,8 @@
       <c r="Y98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z98" s="9" t="n">
-        <v>0</v>
+      <c r="Z98" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA98" s="10" t="n">
         <v>1</v>
@@ -10852,7 +10852,7 @@
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10922,8 +10922,8 @@
       <c r="Y100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z100" s="9" t="n">
-        <v>0</v>
+      <c r="Z100" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA100" s="10" t="n">
         <v>1</v>
@@ -11050,7 +11050,7 @@
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -11120,8 +11120,8 @@
       <c r="Y102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z102" s="9" t="n">
-        <v>0</v>
+      <c r="Z102" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA102" s="10" t="n">
         <v>1</v>
@@ -11644,7 +11644,7 @@
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11714,8 +11714,8 @@
       <c r="Y108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z108" s="9" t="n">
-        <v>0</v>
+      <c r="Z108" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA108" s="10" t="n">
         <v>1</v>
@@ -11842,7 +11842,7 @@
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>10</v>
@@ -11882,8 +11882,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P110" s="9" t="n">
-        <v>3</v>
+      <c r="P110" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q110" s="9" t="n">
         <v>0</v>
@@ -12139,7 +12139,7 @@
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -12209,8 +12209,8 @@
       <c r="Y113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z113" s="9" t="n">
-        <v>0</v>
+      <c r="Z113" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA113" s="10" t="n">
         <v>1</v>
@@ -12832,7 +12832,7 @@
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -12902,8 +12902,8 @@
       <c r="Y120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z120" s="9" t="n">
-        <v>0</v>
+      <c r="Z120" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA120" s="10" t="n">
         <v>1</v>
@@ -13228,7 +13228,7 @@
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -13298,8 +13298,8 @@
       <c r="Y124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z124" s="9" t="n">
-        <v>0</v>
+      <c r="Z124" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA124" s="10" t="n">
         <v>1</v>
@@ -14020,7 +14020,7 @@
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F132" s="6" t="n">
         <v>10</v>
@@ -14034,13 +14034,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>4</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L132" s="7" t="inlineStr">
         <is>
@@ -14078,8 +14078,8 @@
       <c r="U132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V132" s="9" t="n">
-        <v>0</v>
+      <c r="V132" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W132" s="9" t="n">
         <v>0</v>
@@ -14218,7 +14218,7 @@
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F134" s="6" t="n">
         <v>10</v>
@@ -14288,8 +14288,8 @@
       <c r="Y134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z134" s="9" t="n">
-        <v>0</v>
+      <c r="Z134" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA134" s="10" t="n">
         <v>1</v>
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -14486,8 +14486,8 @@
       <c r="Y136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z136" s="9" t="n">
-        <v>0</v>
+      <c r="Z136" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA136" s="10" t="n">
         <v>1</v>
@@ -14614,7 +14614,7 @@
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>10</v>
@@ -14684,8 +14684,8 @@
       <c r="Y138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z138" s="9" t="n">
-        <v>0</v>
+      <c r="Z138" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA138" s="10" t="n">
         <v>1</v>
@@ -15505,7 +15505,7 @@
         </is>
       </c>
       <c r="E147" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F147" s="6" t="n">
         <v>10</v>
@@ -15575,8 +15575,8 @@
       <c r="Y147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z147" s="9" t="n">
-        <v>0</v>
+      <c r="Z147" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA147" s="10" t="n">
         <v>1</v>
@@ -15901,7 +15901,7 @@
         </is>
       </c>
       <c r="E151" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F151" s="6" t="n">
         <v>10</v>
@@ -15971,8 +15971,8 @@
       <c r="Y151" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z151" s="9" t="n">
-        <v>0</v>
+      <c r="Z151" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA151" s="10" t="n">
         <v>1</v>
@@ -16239,7 +16239,7 @@
         </is>
       </c>
       <c r="P154" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q154" s="9" t="n">
         <v>0</v>
@@ -16497,7 +16497,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -16530,7 +16530,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -16563,7 +16563,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -16629,7 +16629,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -16728,7 +16728,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -16761,7 +16761,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -16827,7 +16827,7 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -16959,7 +16959,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -16992,7 +16992,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -17025,7 +17025,7 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -17058,7 +17058,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -17124,7 +17124,7 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -17157,7 +17157,7 @@
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -17190,7 +17190,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -17223,7 +17223,7 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -17256,7 +17256,7 @@
         <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -17289,7 +17289,7 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -17322,7 +17322,7 @@
         <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -17355,7 +17355,7 @@
         <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -17421,7 +17421,7 @@
         <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>0.67</v>
+        <v>1.17</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -17454,7 +17454,7 @@
         <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -17520,7 +17520,7 @@
         <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>

--- a/docs/d/53/inyear.xlsx
+++ b/docs/d/53/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 2 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 2 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 35 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 34 clubs short</t>
         </is>
       </c>
     </row>
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>10</v>
@@ -1064,13 +1064,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
@@ -1108,11 +1108,11 @@
       <c r="U4" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V4" s="9" t="n">
-        <v>3</v>
+      <c r="V4" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W4" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X4" s="10" t="n">
         <v>7</v>
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
@@ -1375,13 +1375,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
@@ -1476,13 +1476,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>0</v>
       </c>
       <c r="V8" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W8" s="9" t="n">
         <v>0</v>
@@ -1577,17 +1577,17 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M9" s="8" t="n">
@@ -1625,7 +1625,7 @@
         <v>4</v>
       </c>
       <c r="W9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9" s="10" t="n">
         <v>6</v>
@@ -1682,13 +1682,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
@@ -1783,17 +1783,17 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M11" s="8" t="n">
@@ -1888,17 +1888,17 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M12" s="8" t="n">
@@ -1993,13 +1993,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
@@ -2397,17 +2397,17 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-40</v>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M17" s="8" t="n">
@@ -2502,13 +2502,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
@@ -2603,13 +2603,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         <v>0</v>
       </c>
       <c r="V19" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W19" s="9" t="n">
         <v>0</v>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>0</v>
       </c>
       <c r="V20" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W20" s="9" t="n">
         <v>0</v>
@@ -2809,13 +2809,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
@@ -2914,13 +2914,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
@@ -3019,13 +3019,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
@@ -3219,17 +3219,17 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M25" s="8" t="n">
@@ -3324,13 +3324,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
@@ -3429,13 +3429,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
@@ -3530,13 +3530,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
@@ -3635,17 +3635,17 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M29" s="8" t="n">
@@ -3740,17 +3740,17 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L30" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M30" s="8" t="n">
@@ -3845,13 +3845,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>0</v>
       </c>
       <c r="V31" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W31" s="9" t="n">
         <v>0</v>
@@ -3946,17 +3946,17 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L32" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>3</v>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M32" s="8" t="n">
@@ -3991,7 +3991,7 @@
         <v>0</v>
       </c>
       <c r="V32" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W32" s="9" t="n">
         <v>0</v>
@@ -4047,13 +4047,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         <v>0</v>
       </c>
       <c r="V34" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W34" s="9" t="n">
         <v>0</v>
@@ -4253,13 +4253,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>0</v>
       </c>
       <c r="V35" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W35" s="9" t="n">
         <v>0</v>
@@ -4354,13 +4354,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
@@ -4455,17 +4455,17 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L37" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L37" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M37" s="8" t="n">
@@ -4560,17 +4560,17 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L38" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L38" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M38" s="8" t="n">
@@ -4710,7 +4710,7 @@
         <v>0</v>
       </c>
       <c r="V39" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W39" s="9" t="n">
         <v>0</v>
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
@@ -4867,13 +4867,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -5028,8 +5028,8 @@
       <c r="Y42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z42" s="9" t="n">
-        <v>0</v>
+      <c r="Z42" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA42" s="10" t="n">
         <v>1</v>
@@ -5071,13 +5071,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
@@ -5172,13 +5172,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
@@ -5277,13 +5277,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         <v>0</v>
       </c>
       <c r="V45" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W45" s="9" t="n">
         <v>0</v>
@@ -5364,7 +5364,7 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>10</v>
@@ -5378,17 +5378,17 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>4</v>
+      </c>
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M46" s="8" t="n">
@@ -5422,11 +5422,11 @@
       <c r="U46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V46" s="9" t="n">
-        <v>0</v>
+      <c r="V46" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W46" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X46" s="10" t="n">
         <v>5</v>
@@ -5469,7 +5469,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5483,13 +5483,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
@@ -5527,8 +5527,8 @@
       <c r="U47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V47" s="9" t="n">
-        <v>3</v>
+      <c r="V47" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W47" s="9" t="n">
         <v>0</v>
@@ -5584,13 +5584,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         <v>0</v>
       </c>
       <c r="S48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T48" s="9" t="n">
         <v>0</v>
@@ -5689,17 +5689,17 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L49" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M49" s="8" t="n">
@@ -5794,13 +5794,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>0</v>
       </c>
       <c r="S50" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T50" s="9" t="n">
         <v>0</v>
@@ -5899,13 +5899,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>0</v>
       </c>
       <c r="V51" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W51" s="9" t="n">
         <v>0</v>
@@ -6004,17 +6004,17 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L52" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L52" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M52" s="8" t="n">
@@ -6109,13 +6109,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
         <v>0</v>
       </c>
       <c r="V53" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W53" s="9" t="n">
         <v>0</v>
@@ -6214,13 +6214,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
@@ -6315,13 +6315,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
@@ -6416,13 +6416,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>0</v>
       </c>
       <c r="V56" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W56" s="9" t="n">
         <v>0</v>
@@ -6521,17 +6521,17 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L57" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L57" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M57" s="8" t="n">
@@ -6626,13 +6626,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
@@ -6671,7 +6671,7 @@
         <v>0</v>
       </c>
       <c r="V58" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W58" s="9" t="n">
         <v>0</v>
@@ -6731,13 +6731,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
@@ -6832,13 +6832,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
@@ -6933,13 +6933,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>4</v>
       </c>
       <c r="W61" s="10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X61" s="10" t="n">
         <v>7</v>
@@ -7137,13 +7137,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
@@ -7238,13 +7238,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
@@ -7283,7 +7283,7 @@
         <v>0</v>
       </c>
       <c r="V64" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W64" s="9" t="n">
         <v>0</v>
@@ -7325,7 +7325,7 @@
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -7339,13 +7339,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
@@ -7383,8 +7383,8 @@
       <c r="U65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V65" s="9" t="n">
-        <v>2</v>
+      <c r="V65" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W65" s="9" t="n">
         <v>0</v>
@@ -7440,17 +7440,17 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L66" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M66" s="8" t="n">
@@ -7545,13 +7545,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
@@ -7646,13 +7646,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
@@ -7747,13 +7747,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
@@ -7848,13 +7848,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
@@ -7949,13 +7949,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
@@ -8050,17 +8050,17 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L72" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M72" s="8" t="n">
@@ -8095,7 +8095,7 @@
         <v>0</v>
       </c>
       <c r="V72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W72" s="9" t="n">
         <v>0</v>
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
@@ -8252,17 +8252,17 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L74" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L74" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M74" s="8" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
@@ -8458,13 +8458,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         <v>0</v>
       </c>
       <c r="V76" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W76" s="9" t="n">
         <v>0</v>
@@ -8559,17 +8559,17 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L77" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L77" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M77" s="8" t="n">
@@ -8660,13 +8660,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8761,13 +8761,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
@@ -8866,17 +8866,17 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L80" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M80" s="8" t="n">
@@ -8911,7 +8911,7 @@
         <v>0</v>
       </c>
       <c r="V80" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W80" s="9" t="n">
         <v>0</v>
@@ -8967,13 +8967,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
@@ -9012,7 +9012,7 @@
         <v>0</v>
       </c>
       <c r="V81" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W81" s="9" t="n">
         <v>0</v>
@@ -9068,13 +9068,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
@@ -9169,13 +9169,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -9274,17 +9274,17 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L84" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L84" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M84" s="8" t="n">
@@ -9301,10 +9301,10 @@
         </is>
       </c>
       <c r="P84" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q84" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R84" s="9" t="n">
         <v>0</v>
@@ -9318,8 +9318,8 @@
       <c r="U84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V84" s="9" t="n">
-        <v>2</v>
+      <c r="V84" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W84" s="9" t="n">
         <v>0</v>
@@ -9379,13 +9379,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
@@ -9478,13 +9478,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L86" s="7" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         <v>0</v>
       </c>
       <c r="V86" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W86" s="9" t="n">
         <v>0</v>
@@ -9565,7 +9565,7 @@
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9579,17 +9579,17 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L87" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L87" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M87" s="8" t="n">
@@ -9617,8 +9617,8 @@
       <c r="S87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T87" s="9" t="n">
-        <v>0</v>
+      <c r="T87" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U87" s="9" t="n">
         <v>0</v>
@@ -9678,13 +9678,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L88" s="7" t="inlineStr">
         <is>
@@ -9723,7 +9723,7 @@
         <v>0</v>
       </c>
       <c r="V88" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W88" s="9" t="n">
         <v>0</v>
@@ -9777,13 +9777,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
@@ -9876,13 +9876,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L90" s="7" t="inlineStr">
         <is>
@@ -9975,13 +9975,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
@@ -10074,13 +10074,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
@@ -10272,13 +10272,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
@@ -10371,17 +10371,17 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L95" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M95" s="8" t="n">
@@ -10470,13 +10470,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -10569,13 +10569,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
@@ -10596,7 +10596,7 @@
         </is>
       </c>
       <c r="P97" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q97" s="9" t="n">
         <v>0</v>
@@ -10668,13 +10668,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
@@ -10767,13 +10767,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
@@ -10812,7 +10812,7 @@
         <v>0</v>
       </c>
       <c r="V99" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W99" s="9" t="n">
         <v>0</v>
@@ -10866,13 +10866,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L100" s="7" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -10965,17 +10965,17 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L101" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L101" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M101" s="8" t="n">
@@ -11003,14 +11003,14 @@
       <c r="S101" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T101" s="9" t="n">
-        <v>0</v>
+      <c r="T101" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U101" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V101" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W101" s="9" t="n">
         <v>0</v>
@@ -11064,13 +11064,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L102" s="7" t="inlineStr">
         <is>
@@ -11109,7 +11109,7 @@
         <v>0</v>
       </c>
       <c r="V102" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W102" s="9" t="n">
         <v>0</v>
@@ -11163,13 +11163,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
@@ -11262,17 +11262,17 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L104" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-19</v>
+      </c>
+      <c r="L104" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M104" s="8" t="n">
@@ -11361,13 +11361,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
@@ -11388,7 +11388,7 @@
         </is>
       </c>
       <c r="P105" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q105" s="9" t="n">
         <v>0</v>
@@ -11460,13 +11460,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="L106" s="7" t="inlineStr">
         <is>
@@ -11559,13 +11559,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L107" s="7" t="inlineStr">
         <is>
@@ -11658,13 +11658,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L108" s="7" t="inlineStr">
         <is>
@@ -11757,13 +11757,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L109" s="7" t="inlineStr">
         <is>
@@ -11856,17 +11856,17 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L110" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-14</v>
+      </c>
+      <c r="L110" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M110" s="8" t="n">
@@ -11955,13 +11955,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
@@ -12054,13 +12054,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L112" s="7" t="inlineStr">
         <is>
@@ -12153,13 +12153,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L113" s="7" t="inlineStr">
         <is>
@@ -12238,7 +12238,7 @@
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -12252,13 +12252,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L114" s="7" t="inlineStr">
         <is>
@@ -12296,8 +12296,8 @@
       <c r="U114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V114" s="9" t="n">
-        <v>3</v>
+      <c r="V114" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W114" s="9" t="n">
         <v>0</v>
@@ -12351,17 +12351,17 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L115" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L115" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M115" s="8" t="n">
@@ -12549,13 +12549,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
@@ -12648,17 +12648,17 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L118" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L118" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M118" s="8" t="n">
@@ -12747,13 +12747,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L119" s="4" t="inlineStr">
         <is>
@@ -12792,7 +12792,7 @@
         <v>0</v>
       </c>
       <c r="V119" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W119" s="9" t="n">
         <v>0</v>
@@ -12846,13 +12846,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L120" s="7" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>0</v>
       </c>
       <c r="V120" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W120" s="9" t="n">
         <v>0</v>
@@ -12945,13 +12945,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
@@ -13044,13 +13044,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L122" s="7" t="inlineStr">
         <is>
@@ -13089,7 +13089,7 @@
         <v>0</v>
       </c>
       <c r="V122" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W122" s="9" t="n">
         <v>0</v>
@@ -13143,13 +13143,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L123" s="4" t="inlineStr">
         <is>
@@ -13188,7 +13188,7 @@
         <v>0</v>
       </c>
       <c r="V123" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W123" s="9" t="n">
         <v>0</v>
@@ -13242,13 +13242,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L124" s="7" t="inlineStr">
         <is>
@@ -13341,13 +13341,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L125" s="7" t="inlineStr">
         <is>
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L126" s="7" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         <v>0</v>
       </c>
       <c r="V126" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W126" s="9" t="n">
         <v>0</v>
@@ -13539,13 +13539,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L127" s="7" t="inlineStr">
         <is>
@@ -13638,13 +13638,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="L128" s="7" t="inlineStr">
         <is>
@@ -13836,17 +13836,17 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L130" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L130" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M130" s="8" t="n">
@@ -13935,13 +13935,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L131" s="4" t="inlineStr">
         <is>
@@ -14034,13 +14034,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>4</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L132" s="7" t="inlineStr">
         <is>
@@ -14133,13 +14133,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L133" s="7" t="inlineStr">
         <is>
@@ -14232,13 +14232,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L134" s="7" t="inlineStr">
         <is>
@@ -14331,17 +14331,17 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L135" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L135" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M135" s="8" t="n">
@@ -14430,13 +14430,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L136" s="7" t="inlineStr">
         <is>
@@ -14529,17 +14529,17 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L137" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L137" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M137" s="8" t="n">
@@ -14628,13 +14628,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L138" s="7" t="inlineStr">
         <is>
@@ -14727,13 +14727,13 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L139" s="7" t="inlineStr">
         <is>
@@ -14826,17 +14826,17 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L140" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L140" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M140" s="8" t="n">
@@ -14925,13 +14925,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L141" s="7" t="inlineStr">
         <is>
@@ -15069,7 +15069,7 @@
         <v>0</v>
       </c>
       <c r="V142" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W142" s="9" t="n">
         <v>0</v>
@@ -15123,13 +15123,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
@@ -15168,7 +15168,7 @@
         <v>0</v>
       </c>
       <c r="V143" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W143" s="9" t="n">
         <v>0</v>
@@ -15222,13 +15222,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L144" s="7" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
         <v>0</v>
       </c>
       <c r="V144" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W144" s="9" t="n">
         <v>0</v>
@@ -15321,13 +15321,13 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J145" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L145" s="4" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>0</v>
       </c>
       <c r="V145" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W145" s="9" t="n">
         <v>0</v>
@@ -15519,13 +15519,13 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L147" s="7" t="inlineStr">
         <is>
@@ -15618,17 +15618,17 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J148" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L148" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L148" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M148" s="8" t="n">
@@ -15717,13 +15717,13 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J149" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L149" s="7" t="inlineStr">
         <is>
@@ -15816,13 +15816,13 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L150" s="7" t="inlineStr">
         <is>
@@ -15915,13 +15915,13 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L151" s="7" t="inlineStr">
         <is>
@@ -16014,13 +16014,13 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J152" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L152" s="7" t="inlineStr">
         <is>
@@ -16113,17 +16113,17 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J153" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L153" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L153" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M153" s="8" t="n">
@@ -16212,17 +16212,17 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L154" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L154" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M154" s="8" t="n">
@@ -16464,7 +16464,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -16512,7 +16512,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -16545,7 +16545,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -16578,7 +16578,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -16644,7 +16644,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -16677,7 +16677,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -16743,7 +16743,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -16761,7 +16761,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -16794,7 +16794,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -16842,7 +16842,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -16875,7 +16875,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -16926,7 +16926,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -16941,7 +16941,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -17007,7 +17007,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -17040,7 +17040,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -17058,7 +17058,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -17073,7 +17073,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -17091,7 +17091,7 @@
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -17106,7 +17106,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -17139,7 +17139,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -17190,7 +17190,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -17205,7 +17205,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -17271,7 +17271,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -17289,7 +17289,7 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -17304,7 +17304,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -17337,7 +17337,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -17403,7 +17403,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -17436,7 +17436,7 @@
         <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -17469,7 +17469,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -17535,7 +17535,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -17568,7 +17568,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/53/inyear.xlsx
+++ b/docs/d/53/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/53/inyear.xlsx
+++ b/docs/d/53/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/53/inyear.xlsx
+++ b/docs/d/53/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/53/inyear.xlsx
+++ b/docs/d/53/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/53/inyear.xlsx
+++ b/docs/d/53/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 2 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 2 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 34 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 34 clubs short</t>
         </is>
       </c>
     </row>
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
@@ -1064,13 +1064,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
@@ -1577,13 +1577,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
@@ -1682,13 +1682,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
@@ -1783,13 +1783,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
@@ -1888,13 +1888,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>0</v>
       </c>
       <c r="V12" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W12" s="9" t="n">
         <v>0</v>
@@ -2914,13 +2914,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
@@ -3740,13 +3740,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
@@ -3845,13 +3845,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
@@ -4047,13 +4047,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4455,17 +4455,17 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>-10</v>
-      </c>
-      <c r="L37" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M37" s="8" t="n">
@@ -4499,8 +4499,8 @@
       <c r="U37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V37" s="9" t="n">
-        <v>3</v>
+      <c r="V37" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W37" s="9" t="n">
         <v>0</v>
@@ -4999,7 +4999,7 @@
         </is>
       </c>
       <c r="P42" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q42" s="9" t="n">
         <v>0</v>
@@ -5172,13 +5172,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>2</v>
       </c>
       <c r="X46" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y46" s="9" t="n">
         <v>0</v>
@@ -6136,7 +6136,7 @@
         </is>
       </c>
       <c r="P53" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q53" s="9" t="n">
         <v>0</v>
@@ -6521,13 +6521,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
@@ -6731,13 +6731,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         <v>1</v>
       </c>
       <c r="Q64" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R64" s="9" t="n">
         <v>0</v>
@@ -7339,13 +7339,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -8288,13 +8288,13 @@
         <v>0</v>
       </c>
       <c r="S74" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T74" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U74" s="9" t="n">
-        <v>0</v>
+      <c r="U74" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V74" s="9" t="n">
         <v>1</v>
@@ -8660,13 +8660,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         <v>0</v>
       </c>
       <c r="Q86" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R86" s="9" t="n">
         <v>0</v>
@@ -9678,13 +9678,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L88" s="7" t="inlineStr">
         <is>
@@ -9723,7 +9723,7 @@
         <v>0</v>
       </c>
       <c r="V88" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W88" s="9" t="n">
         <v>0</v>
@@ -10371,13 +10371,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
@@ -10965,13 +10965,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
@@ -11856,17 +11856,17 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>-14</v>
-      </c>
-      <c r="L110" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-12</v>
+      </c>
+      <c r="L110" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M110" s="8" t="n">
@@ -12252,13 +12252,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L114" s="7" t="inlineStr">
         <is>
@@ -12279,7 +12279,7 @@
         </is>
       </c>
       <c r="P114" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q114" s="9" t="n">
         <v>0</v>
@@ -12351,13 +12351,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>1</v>
       </c>
       <c r="U115" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V115" s="10" t="n">
         <v>4</v>
@@ -12549,13 +12549,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
@@ -12648,13 +12648,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L118" s="7" t="inlineStr">
         <is>
@@ -13044,13 +13044,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L122" s="7" t="inlineStr">
         <is>
@@ -13935,13 +13935,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L131" s="4" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -14162,8 +14162,8 @@
       <c r="P133" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q133" s="9" t="n">
-        <v>1</v>
+      <c r="Q133" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R133" s="9" t="n">
         <v>0</v>
@@ -14515,7 +14515,7 @@
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F137" s="6" t="n">
         <v>10</v>
@@ -14529,17 +14529,17 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="L137" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L137" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M137" s="8" t="n">
@@ -14573,11 +14573,11 @@
       <c r="U137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V137" s="9" t="n">
+      <c r="V137" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W137" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="W137" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="X137" s="10" t="n">
         <v>7</v>
@@ -14727,13 +14727,13 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L139" s="7" t="inlineStr">
         <is>
@@ -14772,7 +14772,7 @@
         <v>0</v>
       </c>
       <c r="V139" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W139" s="9" t="n">
         <v>0</v>
@@ -14812,7 +14812,7 @@
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F140" s="6" t="n">
         <v>10</v>
@@ -14855,8 +14855,8 @@
       <c r="P140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q140" s="9" t="n">
-        <v>1</v>
+      <c r="Q140" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R140" s="9" t="n">
         <v>0</v>
@@ -14925,13 +14925,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L141" s="7" t="inlineStr">
         <is>
@@ -15420,13 +15420,13 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J146" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L146" s="4" t="inlineStr">
         <is>
@@ -15465,7 +15465,7 @@
         <v>0</v>
       </c>
       <c r="V146" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W146" s="9" t="n">
         <v>0</v>
@@ -15717,13 +15717,13 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J149" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="L149" s="7" t="inlineStr">
         <is>
@@ -15915,13 +15915,13 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L151" s="7" t="inlineStr">
         <is>
@@ -16728,7 +16728,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -16743,7 +16743,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -16992,7 +16992,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -17271,7 +17271,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -17421,7 +17421,7 @@
         <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -17454,7 +17454,7 @@
         <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -17469,7 +17469,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">

--- a/docs/d/53/inyear.xlsx
+++ b/docs/d/53/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 2 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 2 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 34 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 34 clubs short</t>
         </is>
       </c>
     </row>
@@ -1064,13 +1064,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
@@ -1169,13 +1169,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
@@ -1476,13 +1476,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
@@ -1888,13 +1888,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
@@ -3019,13 +3019,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F36" s="6" t="n">
         <v>10</v>
@@ -4386,8 +4386,8 @@
       <c r="Q36" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R36" s="9" t="n">
-        <v>1</v>
+      <c r="R36" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S36" s="9" t="n">
         <v>1</v>
@@ -4972,13 +4972,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>0</v>
       </c>
       <c r="V42" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W42" s="9" t="n">
         <v>0</v>
@@ -5483,13 +5483,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         <v>4</v>
       </c>
       <c r="W47" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X47" s="10" t="n">
         <v>4</v>
@@ -6521,13 +6521,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         <v>0</v>
       </c>
       <c r="V57" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W57" s="9" t="n">
         <v>0</v>
@@ -7038,13 +7038,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
@@ -7083,7 +7083,7 @@
         <v>0</v>
       </c>
       <c r="V62" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W62" s="9" t="n">
         <v>0</v>
@@ -8050,13 +8050,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
@@ -8279,7 +8279,7 @@
         </is>
       </c>
       <c r="P74" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q74" s="9" t="n">
         <v>0</v>
@@ -8458,13 +8458,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         <v>0</v>
       </c>
       <c r="S76" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T76" s="9" t="n">
         <v>0</v>
@@ -8503,7 +8503,7 @@
         <v>0</v>
       </c>
       <c r="V76" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W76" s="9" t="n">
         <v>0</v>
@@ -8660,13 +8660,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         </is>
       </c>
       <c r="P79" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q79" s="9" t="n">
         <v>1</v>
@@ -9068,13 +9068,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -9274,17 +9274,17 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L84" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L84" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M84" s="8" t="n">
@@ -9300,8 +9300,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P84" s="9" t="n">
-        <v>3</v>
+      <c r="P84" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q84" s="9" t="n">
         <v>1</v>
@@ -9322,7 +9322,7 @@
         <v>4</v>
       </c>
       <c r="W84" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X84" s="10" t="n">
         <v>7</v>
@@ -9379,13 +9379,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
@@ -9579,13 +9579,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
@@ -9678,13 +9678,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" s="7" t="inlineStr">
         <is>
@@ -9723,7 +9723,7 @@
         <v>0</v>
       </c>
       <c r="V88" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W88" s="9" t="n">
         <v>0</v>
@@ -10074,13 +10074,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
@@ -11166,10 +11166,10 @@
         <v>7</v>
       </c>
       <c r="J103" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
@@ -11757,13 +11757,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L109" s="7" t="inlineStr">
         <is>
@@ -11856,13 +11856,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
@@ -12351,13 +12351,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
@@ -12549,13 +12549,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
@@ -13962,10 +13962,10 @@
         </is>
       </c>
       <c r="P131" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q131" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R131" s="9" t="n">
         <v>0</v>
@@ -15123,13 +15123,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
@@ -15168,7 +15168,7 @@
         <v>0</v>
       </c>
       <c r="V143" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W143" s="9" t="n">
         <v>0</v>
@@ -15222,13 +15222,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L144" s="7" t="inlineStr">
         <is>
@@ -16212,17 +16212,17 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="L154" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-4</v>
+      </c>
+      <c r="L154" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M154" s="8" t="n">
@@ -16695,7 +16695,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -17058,7 +17058,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -17073,7 +17073,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -17568,7 +17568,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
